--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-015_休暇種別管理_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-015_休暇種別管理_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="11372850"/>
+    <ext cx="8572500" cy="11572875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-015 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-015 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="64" customHeight="1">
+    <row r="3" ht="124" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1858,7 +1858,9 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：共通基盤（@EnableMethodSecurity・handleAccessDenied・handleTypeMismatch）の定義元を ONL-001 に統一、handleBadParam を handleTypeMismatch に名称統一、updated_at をトリガ自動更新に変更</t>
+          <t>・確定設計変更 D1〜D10 を反映：共通基盤（@EnableMethodSecurity・handleAccessDenied・handleTypeMismatch）の定義元を ONL-001 に統一、handleBadParam を handleTypeMismatch に名称統一、updated_at をトリガ自動更新に変更
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・年次有給休暇の名称は LeaveTypeService の定数で保持</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -4276,7 +4278,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>コンストラクタインジェクション。操作者IDは不要（監査項目なし）のため Jwt は受け取らない。</t>
+          <t>コンストラクタインジェクション。操作者IDは不要（監査項目なし）のため Authentication は受け取らない。</t>
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
